--- a/tams-invest-parent/tams-invest-asset/src/main/resources/tpl/SppiTest001.xlsx
+++ b/tams-invest-parent/tams-invest-asset/src/main/resources/tpl/SppiTest001.xlsx
@@ -4,13 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14115" windowHeight="2175"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14112" windowHeight="2172"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -31,13 +30,14 @@
     <t>SPPI测试状态</t>
   </si>
   <si>
+    <t>数据来源</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>更新人</t>
-  </si>
-  <si>
-    <t>更新日期</t>
-  </si>
-  <si>
-    <t>数据来源</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -404,18 +404,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37.375" style="1" customWidth="1"/>
-    <col min="3" max="5" width="19.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.875" customWidth="1"/>
-    <col min="9" max="9" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" style="1" customWidth="1"/>
+    <col min="3" max="5" width="19.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -426,16 +426,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
